--- a/excel-files/MANILA/TONDO HIGH SCHOOL.xlsx
+++ b/excel-files/MANILA/TONDO HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{883E31A4-3CA9-4726-A78E-C5BB2E00609A}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C41DC58-B49A-416A-B992-AC90B82CF917}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3509,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3546,7 +3546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:8" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3646,12 +3646,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:8" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3751,12 +3751,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:8" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3886,7 +3886,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:8" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4076,7 +4076,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4266,7 +4266,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4696,7 +4696,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5549,53 +5549,6 @@
         <v>118</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1"/>
-    <row r="100" spans="1:8" hidden="1"/>
-    <row r="101" spans="1:8" hidden="1"/>
-    <row r="102" spans="1:8" hidden="1"/>
-    <row r="103" spans="1:8" hidden="1"/>
-    <row r="104" spans="1:8" hidden="1"/>
-    <row r="105" spans="1:8" hidden="1"/>
-    <row r="106" spans="1:8" hidden="1"/>
-    <row r="107" spans="1:8" hidden="1"/>
-    <row r="108" spans="1:8" hidden="1"/>
-    <row r="109" spans="1:8" hidden="1"/>
-    <row r="110" spans="1:8" hidden="1"/>
-    <row r="111" spans="1:8" hidden="1"/>
-    <row r="112" spans="1:8" hidden="1"/>
-    <row r="113" hidden="1"/>
-    <row r="114" hidden="1"/>
-    <row r="115" hidden="1"/>
-    <row r="116" hidden="1"/>
-    <row r="117" hidden="1"/>
-    <row r="118" hidden="1"/>
-    <row r="119" hidden="1"/>
-    <row r="120" hidden="1"/>
-    <row r="121" hidden="1"/>
-    <row r="122" hidden="1"/>
-    <row r="123" hidden="1"/>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1"/>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1"/>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1"/>
-    <row r="130" hidden="1"/>
-    <row r="131" hidden="1"/>
-    <row r="132" hidden="1"/>
-    <row r="133" hidden="1"/>
-    <row r="134" hidden="1"/>
-    <row r="135" hidden="1"/>
-    <row r="136" hidden="1"/>
-    <row r="137" hidden="1"/>
-    <row r="138" hidden="1"/>
-    <row r="139" hidden="1"/>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1"/>
-    <row r="142" hidden="1"/>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1"/>
-    <row r="145" hidden="1"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C1:E50 E51:E64 C51:C64 C65:E98" name="Textbooks"/>
@@ -5603,8 +5556,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5619,7 +5572,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5765,7 +5718,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" hidden="1" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>61</v>
       </c>
@@ -5832,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5844,7 +5797,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5913,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5982,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6051,7 +6004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6120,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6189,7 +6142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6258,7 +6211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6327,7 +6280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6396,7 +6349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6409,7 +6362,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6478,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6547,7 +6500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6616,7 +6569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6685,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6754,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6823,7 +6776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6892,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6961,7 +6914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6975,7 +6928,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7044,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7113,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7182,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7251,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7320,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7389,7 +7342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7458,7 +7411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7527,7 +7480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7596,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7610,7 +7563,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7679,7 +7632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7748,7 +7701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7817,7 +7770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7886,7 +7839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7955,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8024,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8093,7 +8046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8162,7 +8115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8231,7 +8184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8245,7 +8198,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8314,7 +8267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8383,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8452,7 +8405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8521,7 +8474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8590,7 +8543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8659,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8728,7 +8681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8797,7 +8750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8866,7 +8819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8880,7 +8833,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8949,7 +8902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9018,7 +8971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9087,7 +9040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9156,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9225,7 +9178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9294,7 +9247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9363,7 +9316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9432,7 +9385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9501,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -10136,7 +10089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10771,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -11406,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -12041,7 +11994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12607,7 +12560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12618,7 +12571,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12680,7 +12633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="113" spans="1:27" ht="19.149999999999999">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12742,7 +12695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="114" spans="1:27" ht="19.149999999999999">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12804,7 +12757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="115" spans="1:27" ht="19.149999999999999">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12866,7 +12819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="116" spans="1:27" ht="19.149999999999999">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12928,7 +12881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="117" spans="1:27" ht="19.149999999999999">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12990,7 +12943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="118" spans="1:27" ht="19.149999999999999">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13052,7 +13005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="119" spans="1:27" ht="19.149999999999999">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13114,7 +13067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="120" spans="1:27" ht="19.149999999999999">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13176,7 +13129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="121" spans="1:27" ht="19.149999999999999">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13238,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="122" spans="1:27" ht="19.149999999999999">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13300,7 +13253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="123" spans="1:27" ht="19.149999999999999">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13362,7 +13315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="124" spans="1:27" ht="19.149999999999999">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13424,7 +13377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="125" spans="1:27" ht="19.149999999999999">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13486,7 +13439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="126" spans="1:27" ht="19.149999999999999">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13548,7 +13501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="127" spans="1:27" ht="19.149999999999999">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13605,186 +13558,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13804,8 +13577,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13823,7 +13596,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13969,7 +13742,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="3" spans="1:27" ht="19.149999999999999">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14038,7 +13811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" ht="19.149999999999999">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14107,7 +13880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14176,7 +13949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14245,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14314,7 +14087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14383,7 +14156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14452,7 +14225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14521,8 +14294,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14591,7 +14364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14660,7 +14433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14729,7 +14502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14798,7 +14571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14867,7 +14640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14936,7 +14709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15005,7 +14778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15074,8 +14847,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15144,7 +14917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15213,7 +14986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15282,7 +15055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15351,7 +15124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15420,7 +15193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15489,7 +15262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15558,7 +15331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15627,7 +15400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15696,8 +15469,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15766,7 +15539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15835,7 +15608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15904,7 +15677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15973,7 +15746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16042,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16111,7 +15884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16180,7 +15953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16249,7 +16022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16318,7 +16091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16387,7 +16160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16456,8 +16229,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16526,7 +16299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16595,7 +16368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16664,7 +16437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16733,7 +16506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16802,7 +16575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16871,7 +16644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16940,7 +16713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17009,7 +16782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17078,7 +16851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17147,7 +16920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17216,8 +16989,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17286,7 +17059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17355,7 +17128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17424,7 +17197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17493,7 +17266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17562,7 +17335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17631,7 +17404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17700,7 +17473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17769,7 +17542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17838,7 +17611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17907,7 +17680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17976,7 +17749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1" hidden="1"/>
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
     <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
@@ -18758,7 +18531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" hidden="1"/>
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
     <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
@@ -19540,7 +19313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" hidden="1"/>
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
     <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
@@ -20358,7 +20131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" hidden="1"/>
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
     <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
@@ -21192,7 +20965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" hidden="1"/>
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
         <v>24</v>
@@ -21745,8 +21518,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1" hidden="1"/>
-    <row r="124" spans="1:28" hidden="1">
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="124" spans="1:28">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21776,7 +21549,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28" hidden="1">
+    <row r="125" spans="1:28">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21806,7 +21579,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28" hidden="1">
+    <row r="126" spans="1:28">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21836,7 +21609,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28" hidden="1">
+    <row r="127" spans="1:28">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21866,7 +21639,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28" hidden="1">
+    <row r="128" spans="1:28">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21896,7 +21669,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28" hidden="1">
+    <row r="129" spans="1:28">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21926,7 +21699,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28" hidden="1">
+    <row r="130" spans="1:28">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21956,7 +21729,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28" hidden="1">
+    <row r="131" spans="1:28">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21986,7 +21759,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28" hidden="1">
+    <row r="132" spans="1:28">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -22016,7 +21789,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28" hidden="1">
+    <row r="133" spans="1:28">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -22046,7 +21819,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28" hidden="1">
+    <row r="134" spans="1:28">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -22076,7 +21849,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28" hidden="1">
+    <row r="135" spans="1:28">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -22106,7 +21879,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28" hidden="1">
+    <row r="136" spans="1:28">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -22136,7 +21909,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28" hidden="1">
+    <row r="137" spans="1:28">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -22166,7 +21939,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28" hidden="1">
+    <row r="138" spans="1:28">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -22196,7 +21969,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28" hidden="1">
+    <row r="139" spans="1:28">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22226,7 +21999,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28" hidden="1">
+    <row r="140" spans="1:28">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -22256,186 +22029,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C67:C77 C79:C89 C91:C101 C103:C113" name="Textbooks"/>
@@ -22453,8 +22046,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
